--- a/KeywordDrivenTest/_Report/ExcelReport_Login.xlsx
+++ b/KeywordDrivenTest/_Report/ExcelReport_Login.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -81,6 +81,14 @@
   </si>
   <si>
     <t>loginButton</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no such window: target window already closed
+from unknown error: web view not found
+  (Session info: chrome=133.0.6943.54)</t>
   </si>
   <si>
     <t>Step5</t>
@@ -114,7 +122,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -124,6 +132,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF008000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -139,10 +152,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" applyFont="1" fillId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="3" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -265,11 +279,11 @@
       <c r="E5" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>12</v>
+      <c r="F5" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -277,22 +291,22 @@
         <v>7</v>
       </c>
       <c r="B6" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="G6" s="0" t="s">
         <v>24</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="0" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/KeywordDrivenTest/_Report/ExcelReport_Login.xlsx
+++ b/KeywordDrivenTest/_Report/ExcelReport_Login.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -65,6 +65,12 @@
     <t>mazhar.karim@brainstation-23.com</t>
   </si>
   <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Failed to send values to the element after multiple attempts</t>
+  </si>
+  <si>
     <t>Step3</t>
   </si>
   <si>
@@ -83,12 +89,7 @@
     <t>loginButton</t>
   </si>
   <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no such window: target window already closed
-from unknown error: web view not found
-  (Session info: chrome=133.0.6943.54)</t>
+    <t>Failed to click the element after multiple attempts</t>
   </si>
   <si>
     <t>Step5</t>
@@ -233,11 +234,11 @@
       <c r="E3" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>12</v>
+      <c r="F3" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -245,22 +246,22 @@
         <v>7</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="0" t="s">
         <v>18</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="0" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -268,22 +269,22 @@
         <v>7</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -291,22 +292,22 @@
         <v>7</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>23</v>
+        <v>28</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
